--- a/data/seed/portfolio/L-2024-8836/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-8836/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,202 +535,202 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>12672000</v>
+        <v>17772000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oydin Polimer MChJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>371571313</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000651931544001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №163/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №3/26 от 02.07.2026</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>70372000</v>
+        <v>75472000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>6192000</v>
+        <v>3384000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №98/26 от 01.07.2026</t>
+          <t>Оплата по счет-фактуре №1349 за поставленный товар</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>76564000</v>
+        <v>78856000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>1899000</v>
+        <v>1182000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6370 02.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №3039 за поставленный товар</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>78463000</v>
+        <v>80038000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>1808000</v>
+        <v>3009000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4520 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №2742 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>80271000</v>
+        <v>83047000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>3180000</v>
+        <v>1112000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №257/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №229/26, НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>83451000</v>
+        <v>84159000</v>
       </c>
     </row>
     <row r="13">
@@ -742,35 +742,35 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>6285000</v>
+        <v>932000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oydin Polimer MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>371571313</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000651931544001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №252/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №12/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>89736000</v>
+        <v>85091000</v>
       </c>
     </row>
     <row r="14">
@@ -780,432 +780,432 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>3421000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>11355000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>292526909</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №109/26, QQS 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>93157000</v>
+        <v>73736000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>2100000</v>
+        <v>3555000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oydin Polimer MChJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>371571313</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000651931544001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №1890 за поставленный товар</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>95257000</v>
+        <v>77291000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>6362000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>1305000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №118/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №1007 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>88895000</v>
+        <v>78596000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>11355000</v>
+        <v>1057000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>228757201</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000059102912001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Аренда помещения за июль, дог. №39/22</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>77540000</v>
+        <v>77539000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>1770000</v>
+        <v>1012000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oydin Polimer MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>371571313</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000651931544001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №281/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №6395 за поставленный товар</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>79310000</v>
+        <v>78551000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>24498000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>936000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Andijon Tikuv XK</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>394646097</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000219340318001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №205/26</t>
+          <t>Оплата за продукцию по договору №263/26, НДС 12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>54812000</v>
+        <v>79487000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1057000</v>
+        <v>18593000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Farg'ona Qurilish MChJ</t>
+          <t>Qarshi Yog'och MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>328270750</t>
+          <t>229836792</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000064340974001</t>
+          <t>20208000320154101001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartn. №47/22</t>
+          <t>Оплата за товары согласно счет-фактуре №5952</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>53755000</v>
+        <v>60894000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>17284000</v>
+        <v>1319000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shartnoma №114/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №3091 за поставленный товар</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>71039000</v>
+        <v>62213000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>5765000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>13109000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №91/26 от 09.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №171/26, НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>65274000</v>
+        <v>75322000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>5659000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>4410000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5256</t>
+          <t>Оплата за продукцию по дог. №160/26, НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>59615000</v>
+        <v>79732000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>22967000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>1675000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Andijon Tikuv XK</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>394646097</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000219340318001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5825</t>
+          <t>Оплата за продукцию по договору №114/26, НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>36648000</v>
+        <v>81407000</v>
       </c>
     </row>
     <row r="25">
@@ -1217,35 +1217,35 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>1873000</v>
+        <v>1125000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6801 13.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9354</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>38521000</v>
+        <v>82532000</v>
       </c>
     </row>
     <row r="26">
@@ -1256,76 +1256,76 @@
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10386000</v>
+        <v>41268000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>324427874</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000486397523001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №84/26 от 13.07.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №2431</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>28135000</v>
+        <v>41264000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>3934000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>7320000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tong Trans Servis MChJ</t>
+          <t>Bunyodkor Tur Servis XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>278238360</t>
+          <t>200087767</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000935657565001</t>
+          <t>20208000805195969001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Shartnoma №262/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №16/26 от 14.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>32069000</v>
+        <v>33944000</v>
       </c>
     </row>
     <row r="28">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>22669000</v>
+        <v>24544000</v>
       </c>
     </row>
     <row r="29">
@@ -1370,37 +1370,37 @@
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>1548000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>8433000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Предоплата за товар по договору №24/26 от 16.07.2026</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>21121000</v>
+        <v>32977000</v>
       </c>
     </row>
     <row r="30">
@@ -1410,1093 +1410,1098 @@
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>1548000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>1180000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I IYUN 2026</t>
+          <t>Оплата за продукцию по дог. №279/26, НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>19573000</v>
+        <v>34157000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>2944000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>1548000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9940 17.07.2026, QQS bilan</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22517000</v>
+        <v>32609000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46223</v>
+        <v>46219</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>13379000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>1548000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Shartnoma №80/26 bo'yicha oldindan to'lov</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35896000</v>
+        <v>31061000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>10128000</v>
+        <v>1133000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №262/26, QQS 12%</t>
+          <t>ОПЛАТА ПО С/Ф №8298 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46024000</v>
+        <v>32194000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>1759000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>11980000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>324427874</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000486397523001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Shartnoma №235/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по дог. №261/26 от 17.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>47783000</v>
+        <v>20214000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>4478000</v>
+        <v>40222000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №18/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №238/26, QQS 12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>52261000</v>
+        <v>60436000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>1669000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>2569000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Olmaliq Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>277730365</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000484312632001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Оплата за продукцию по договору №231/26, НДС 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>50592000</v>
+        <v>63005000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>10286000</v>
+        <v>3208000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №39/26 от 22.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6522</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>60878000</v>
+        <v>66213000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>6486000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>2031000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №273/26</t>
+          <t>Оплата за продукцию по договору №155/26, НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>54392000</v>
+        <v>68244000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>9040000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>1521000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8104</t>
+          <t>Предоплата за товар по дог. №50/26 от 21.07.2026</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>45352000</v>
+        <v>69765000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>12631000</v>
+        <v>918000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Oydin Yog'och MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>297579070</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000741377616001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №226/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №231/26 от 21.07.2026</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>57983000</v>
+        <v>70683000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>6418000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>5171000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4483 27.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно с/ф №3884</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>64401000</v>
+        <v>65512000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>5460000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>22833000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>324427874</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000486397523001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №256/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №20/26 от 21.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>69861000</v>
+        <v>42679000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>3614000</v>
+        <v>12601000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shodlik Metall Servis MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>396420026</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000774104398001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Shartnoma 207/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №145/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>73475000</v>
+        <v>55280000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>2111000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>1698000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Shartnoma №53/26 bo'yicha oldindan to'lov</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>75586000</v>
+        <v>53582000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>661000</v>
+        <v>5766000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Qarshi Yog'och MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>229836792</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000433750334001</t>
+          <t>20208000320154101001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за сырье по договору №91/26 от 23.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>74925000</v>
+        <v>47816000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>17870000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>1047000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Andijon Tikuv XK</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>394646097</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000219340318001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6237</t>
+          <t>Оплата по с/ф №3280 за поставленный товар</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>57055000</v>
+        <v>48863000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>3470000</v>
+        <v>1392000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7797 30.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №294/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>60525000</v>
+        <v>50255000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>11311000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>1200000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №133/26, QQS bilan</t>
+          <t>Оплата по с/ф №9096 за поставленный товар</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>49214000</v>
+        <v>51455000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>300000</v>
+        <v>661000</v>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000268276133001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>48914000</v>
+        <v>50794000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>13801000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>6095000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Termiz Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>291603301</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000457033251001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №253/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №91/26</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>62715000</v>
+        <v>44699000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>10009000</v>
+        <v>1175000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №764 за поставленный товар</t>
+          <t>Shartnoma №273/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>72724000</v>
+        <v>45874000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>40618000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>1326000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6986</t>
+          <t>Mahsulot uchun to'lov, shartnoma №23/26, QQS 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>32106000</v>
+        <v>47200000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46239</v>
+        <v>46232</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>18252000</v>
+        <v>857000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2221 05.08.2026, QQS bilan</t>
+          <t>Shartnoma №260/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>50358000</v>
+        <v>48057000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46239</v>
+        <v>46232</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>14109000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>766000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Barakali Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №5674</t>
+          <t>Оплата за продукцию по договору №72/26, НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>36249000</v>
+        <v>48823000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46240</v>
+        <v>46233</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>4648000</v>
+        <v>2480000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №217/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №255/26 от 30.07.2026</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>40897000</v>
+        <v>51303000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>5316000</v>
+        <v>1593000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Oqtosh Agro Servis AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>377454634</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000442071878001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7710</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8234 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46213000</v>
+        <v>52896000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>4289000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>306225664</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2506,37 +2511,37 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №165/26, НДС 12%</t>
+          <t>ПЛАТА ЗА SMS-ИНФОРМИРОВНИЕ</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>50502000</v>
+        <v>52596000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>8032000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>2846000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2546,872 +2551,867 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №217/26 от 10.08.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №6958</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>58534000</v>
+        <v>49750000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>5426000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>4766000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Shartnoma №207/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по дог. №97/26 от 04.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>63960000</v>
+        <v>44984000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1314000</v>
+        <v>14109000</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Farg'ona Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>328270750</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000064340974001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №3879</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>62646000</v>
+        <v>30875000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>5382000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>10070000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari AJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>328661276</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000139218238001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3597</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2241</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>57264000</v>
+        <v>40945000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>28693000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>2882000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №171/26</t>
+          <t>Предоплата за товар по договору №181/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28571000</v>
+        <v>43827000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>6098000</v>
+        <v>2622000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Shartnoma №15/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по дог. №169/26, НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>34669000</v>
+        <v>46449000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>5410000</v>
+        <v>3666000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Bahor Metall MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>211585574</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000892994714001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №10/26</t>
+          <t>Оплата за сырье по договору №184/26 от 06.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>29259000</v>
+        <v>42783000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>5280000</v>
+        <v>2618000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Termiz Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>291603301</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000457033251001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4666</t>
+          <t>Оплата за товары согласно счет-фактуре №5632</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>23979000</v>
+        <v>40165000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>15309000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>11370000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №253/26</t>
+          <t>Оплата за товар по счет-фактуре 7128 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>8670000</v>
+        <v>51535000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>1924000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>5235000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Оплата по счет-фактуре №2695 за поставленный товар</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6746000</v>
+        <v>56770000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>1924000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>2425000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Оплата за товар по счет-фактуре №6031 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>4822000</v>
+        <v>59195000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46249</v>
+        <v>46244</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>9400000</v>
+        <v>1314000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8836)</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>228757201</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>16307000388652287417</t>
+          <t>20208000059102912001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8836 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>-4578000</v>
+        <v>57881000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>27271000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>2906000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oydin Polimer MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>371571313</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000651931544001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8178</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №257/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>22693000</v>
+        <v>54975000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>12799000</v>
+        <v>7379000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari AJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>328661276</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000139218238001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №108/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №515</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>9894000</v>
+        <v>47596000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>4446000</v>
+        <v>8145000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4232</t>
+          <t>Оплата за товары согласно счет-фактуре №1595</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5448000</v>
+        <v>39451000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46253</v>
+        <v>46246</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>9789000</v>
+        <v>2695000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №6291 за поставленный товар</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>15237000</v>
+        <v>42146000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46253</v>
+        <v>46246</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>6464000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>4381000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Bahor Metall MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>211585574</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000892994714001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6416</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №190/26, QQS bilan</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>21701000</v>
+        <v>37765000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>3746000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>8771000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №237/26</t>
+          <t>Оплата за товар по счет-фактуре №7895 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>17955000</v>
+        <v>46536000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>10454000</v>
+        <v>3622000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari AJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>328661276</t>
+          <t>324427874</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000139218238001</t>
+          <t>20208000486397523001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №60/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №198/26</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>7501000</v>
+        <v>42914000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>12822000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>7923000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oydin Polimer MChJ</t>
+          <t>Termiz Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>371571313</t>
+          <t>291603301</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000651931544001</t>
+          <t>20208000457033251001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №163/26, QQS 12%</t>
+          <t>Оплата за товары согласно с/ф №8969</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>20323000</v>
+        <v>34991000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46255</v>
+        <v>46249</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>9796000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>292526909</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8836)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>16307000388652287417</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №108/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-8836 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>30119000</v>
+        <v>25591000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46255</v>
+        <v>46251</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>2201000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>5613000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №91/26 ОТ 17.08.2026</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>27918000</v>
+        <v>31204000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>821000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>4097000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000433750334001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3421,747 +3421,757 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за товар по счет-фактуре №9067 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>27097000</v>
+        <v>35301000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>11131000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>1946000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №158/26, QQS BILAN</t>
+          <t>Оплата по счет-фактуре №7308 за поставленный товар</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>15966000</v>
+        <v>37247000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>35849000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>1924000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Shartnoma №116/26 bo'yicha oldindan to'lov</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>51815000</v>
+        <v>35323000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>5559000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>1924000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4838 за поставленный товар</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>57374000</v>
+        <v>33399000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46265</v>
+        <v>46252</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>7995000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Barakali Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Предоплата за товар по договору №225/26 от 18.08.2026</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>57074000</v>
+        <v>41394000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>8298000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>3476000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №155/26 от 31.08.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7353</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>48776000</v>
+        <v>44870000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46267</v>
+        <v>46253</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>2053000</v>
+        <v>3345000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №216/26, QQS 12%</t>
+          <t>Оплата по с/ф №5674 за поставленный товар</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>50829000</v>
+        <v>48215000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46267</v>
+        <v>46254</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>1518000</v>
+        <v>4387000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №139/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №34/26, НДС 12%</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>52347000</v>
+        <v>52602000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46268</v>
+        <v>46254</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>5075000</v>
+        <v>2225000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №126/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №4487 за поставленный товар</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>57422000</v>
+        <v>54827000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46269</v>
+        <v>46255</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>11223000</v>
+        <v>4451000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №288/26 от 04.09.2026</t>
+          <t>Оплата по счет-фактуре №6436 за поставленный товар</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>68645000</v>
+        <v>59278000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46269</v>
+        <v>46255</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>5204000</v>
+        <v>3613000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tong Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>278238360</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000935657565001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2656 04.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №224/26 от 21.08.2026</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>73849000</v>
+        <v>62891000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46269</v>
+        <v>46255</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>2053000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>2098000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Shartnoma №183/26 bo'yicha oldindan to'lov</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>75902000</v>
+        <v>60793000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46269</v>
+        <v>46255</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>1674000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>5167000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №243/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №103/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>77576000</v>
+        <v>55626000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46272</v>
+        <v>46255</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>5263000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>70489000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №164/26, QQS 12%</t>
+          <t>Оплата за сырье по дог. №72/26 от 21.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>82839000</v>
+        <v>-14863000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>1484000</v>
+        <v>47072000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7094 07.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №163/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>84323000</v>
+        <v>32209000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>1244000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>18138000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Farg'ona Qurilish MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>328270750</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000064340974001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Оплата за продукцию по договору №115/26, НДС 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>83079000</v>
+        <v>50347000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>4717000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>6126000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №227/26</t>
+          <t>Оплата за продукцию по дог. №126/26, НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>78362000</v>
+        <v>56473000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>6111000</v>
+        <v>821000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>307251411</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000907982820001</t>
+          <t>20208000268276133001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №271/26, QQS bilan</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>72251000</v>
+        <v>55652000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>13030000</v>
+        <v>2592000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Kamalak Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>202984873</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000476179703001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №290/26, QQS BILAN</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №244/26</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>59221000</v>
+        <v>53060000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>13359000</v>
+        <v>5541000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Kamalak Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4171,672 +4181,667 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Оплата за товары согласно счет-фактуре №995</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>45862000</v>
+        <v>47519000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46273</v>
+        <v>46260</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>13783000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>1764000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Bahor Metall MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>211585574</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000892994714001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №278/26, НДС 12%</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №97/26</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>59645000</v>
+        <v>45755000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46273</v>
+        <v>46260</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>4888000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>3378000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Termiz Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>291603301</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000457033251001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1244</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №99/26</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>64533000</v>
+        <v>42377000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46273</v>
+        <v>46261</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>3244000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>3871000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Termiz Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>291603301</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000457033251001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1299 08.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №178/26</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>67777000</v>
+        <v>38506000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>2598000</v>
+        <v>3320000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9438 ОТ 08.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №8773 за поставленный товар</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>70375000</v>
+        <v>41826000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46274</v>
+        <v>46262</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>6211000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>8851000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lo, shartnoma №286/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по дог. №30/26</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>76586000</v>
+        <v>32975000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>1491000</v>
+        <v>12991000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №251/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №6705 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>78077000</v>
+        <v>45966000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>3455000</v>
+        <v>300000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>286774546</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №116/26</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>74622000</v>
+        <v>45666000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>10678000</v>
+        <v>3065000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Oqtosh Agro Servis AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>377454634</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000442071878001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Shartnoma №219/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №110/26, НДС 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>85300000</v>
+        <v>48731000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>20768000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>18151000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nukus Mehmonxona AJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>306225664</t>
+          <t>324427874</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000851180527001</t>
+          <t>20208000486397523001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Shartnoma №220/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №291/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>106068000</v>
+        <v>30580000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>7986000</v>
+        <v>19024000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>342002687</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000410439874001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2663 14.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №2557 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>114054000</v>
+        <v>49604000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>4835000</v>
+        <v>8641000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SHARTNOMA №122/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за товар по счет-фактуре №2549 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>118889000</v>
+        <v>58245000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>9291000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>4164000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Andijon Tikuv XK</t>
+          <t>Shodlik Yog' Zavodi XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>394646097</t>
+          <t>323836039</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000219340318001</t>
+          <t>20208000565756543001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №102/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №128/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>109598000</v>
+        <v>62409000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>11310000</v>
+        <v>3914000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oydin Polimer MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>371571313</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000651931544001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SHARTNOMA №224/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за товар по счет-фактуре №4129 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>120908000</v>
+        <v>66323000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>2839000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8836)</t>
+          <t>Shodlik Yog' Zavodi XK</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>323836039</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>16307000388652287417</t>
+          <t>20208000565756543001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8836 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за продукцию по дог. №35/26, НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>111508000</v>
+        <v>69162000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>1822000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>1395000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>Предоплата за товар по дог. №218/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>109686000</v>
+        <v>70557000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>1822000</v>
+        <v>13359000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №5610</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>107864000</v>
+        <v>57198000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46282</v>
+        <v>46273</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>2682000</v>
+        <v>5363000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Qarshi Yog'och MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>229836792</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000320154101001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4846,117 +4851,117 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №236/26 от 17.09.2026, НДС 12%</t>
+          <t>Предоплата за материалы по дог. №55/26</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>105182000</v>
+        <v>51835000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46282</v>
+        <v>46274</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>3801000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>2804000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №151/26</t>
+          <t>Оплата за продукцию по дог. №133/26, НДС 12%</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>101381000</v>
+        <v>54639000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>7157000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>1244000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shodlik Metall Servis MChJ</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>396420026</t>
+          <t>228757201</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000774104398001</t>
+          <t>20208000059102912001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8966</t>
+          <t>Аренда помещения за сентябрь, дог. №39/22</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>108538000</v>
+        <v>53395000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>4941000</v>
+        <v>1097000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Nihol Savdo AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>270750806</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000340974643001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4966,357 +4971,352 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4756 21.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №204/26 от 10.09.2026</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>113479000</v>
+        <v>54492000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>1565000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>12822000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Bahor Metall MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>211585574</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000892994714001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5631 21.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №255/26</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>115044000</v>
+        <v>41670000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>2054000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>6117000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Оплата за товар по счет-фактуре №3182 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>112990000</v>
+        <v>47787000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>5574000</v>
+        <v>1822000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Andijon Tikuv XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>394646097</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000219340318001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №284/26</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>107416000</v>
+        <v>45965000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>9899000</v>
+        <v>1822000</v>
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Andijon Tikuv XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>394646097</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000219340318001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №288/26</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>97517000</v>
+        <v>44143000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>29530000</v>
+        <v>13025000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №120/26</t>
+          <t>Предоплата за материалы по договору №85/26</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>67987000</v>
+        <v>31118000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46287</v>
+        <v>46279</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>2645000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>34597000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Kamalak Sut MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №151/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №24/26</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>70632000</v>
+        <v>-3479000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46289</v>
+        <v>46280</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>1504000</v>
+        <v>2355000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>257131346</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000193154440001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3443</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4372 ОТ 15.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>72136000</v>
+        <v>-1124000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46289</v>
+        <v>46280</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>1483000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>292526909</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8836)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>16307000388652287417</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9382</t>
+          <t>Kredit shartnomasi L-2024-8836 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>73619000</v>
+        <v>-10524000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>778000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>4228000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000433750334001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5326,432 +5326,437 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Tovar uchun to'lov, h/f №7380 16.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>72841000</v>
+        <v>-6296000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>14172000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>1247000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №293/26, QQS bilan</t>
+          <t>Оплата по с/ф №2786 за поставленный товар</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>58669000</v>
+        <v>-5049000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46290</v>
+        <v>46282</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>4458000</v>
+        <v>2686000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №271/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №151/26, QQS 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>63127000</v>
+        <v>-2363000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46293</v>
+        <v>46283</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>5167000</v>
+        <v>1100000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Barakali Tur Servis AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>252690949</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000947475997001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4634 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №75/26, НДС 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>68294000</v>
+        <v>-1263000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>4009000</v>
+        <v>14117000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Jizzax Trans Servis AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>264609702</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000934031863001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6660</t>
+          <t>Предоплата за товар по договору №239/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>72303000</v>
+        <v>12854000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>2728000</v>
+        <v>4494000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oydin Polimer MChJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>371571313</t>
+          <t>257131346</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000651931544001</t>
+          <t>20208000193154440001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Shartnoma №24/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5569</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>75031000</v>
+        <v>17348000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>2649000</v>
+        <v>1858000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shodlik Metall Servis MChJ</t>
+          <t>Olmaliq Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>396420026</t>
+          <t>277730365</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000774104398001</t>
+          <t>20208000484312632001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №92/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №6894 за поставленный товар</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>77680000</v>
+        <v>19206000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>2228000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>2073000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shodlik Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>396420026</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000774104398001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №201/26, QQS 12%</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>79908000</v>
+        <v>17133000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>10511000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>22731000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall MChJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>286774546</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000424420718001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3572</t>
+          <t>Оплата за продукцию по договору №290/26, НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>69397000</v>
+        <v>39864000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>21151000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>3681000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Andijon Oziq-ovqat Savdo AJ</t>
+          <t>Denov Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>204483181</t>
+          <t>322566418</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000414062405001</t>
+          <t>20208000118052744001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №107/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №3182 от 24.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>48246000</v>
+        <v>43545000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46294</v>
+        <v>46290</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>7263000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>778000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>292526909</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000969474759001</t>
+          <t>20208000268276133001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №252/26, QQS 12%</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>55509000</v>
+        <v>42767000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>300000</v>
+        <v>3722000</v>
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Kamalak Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>216334991</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000943927480001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5761,76 +5766,351 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за упаковочные материалы, с/ф №4827</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>55209000</v>
+        <v>39045000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>6909000</v>
+        <v>5919000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>303975790</t>
+          <t>324427874</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000057413776001</t>
+          <t>20208000486397523001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2840</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №180/26, QQS bilan</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
+        <v>33126000</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B141" t="n">
+        <v>233</v>
+      </c>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>27931000</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Shodlik Yog' Zavodi XK</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>323836039</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>20208000565756543001</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №9084 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>61057000</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B142" t="n">
+        <v>234</v>
+      </c>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>20793000</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Denov Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>322566418</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>20208000118052744001</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №272/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>81850000</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B143" t="n">
+        <v>235</v>
+      </c>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>6253000</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Oydin Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>297579070</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>20208000741377616001</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №232/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>88103000</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B144" t="n">
+        <v>236</v>
+      </c>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>1358000</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Barakali Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>252690949</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>20208000947475997001</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №13/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>89461000</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B145" t="n">
+        <v>237</v>
+      </c>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>4830000</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Barakali Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>252690949</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>20208000947475997001</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №226/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>94291000</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B146" t="n">
+        <v>238</v>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Navbahor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>93991000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B147" t="n">
+        <v>239</v>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>45691000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Kamalak Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>216334991</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000943927480001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №247/26, QQS BILAN</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
         <v>48300000</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C141" s="4" t="n">
-        <v>503053000</v>
-      </c>
-      <c r="D141" s="4" t="n">
-        <v>493653000</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="C148" s="4" t="n">
+        <v>498476000</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>489076000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C142" s="4" t="n">
+      <c r="C149" s="4" t="n">
         <v>48300000</v>
       </c>
-      <c r="D142" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
